--- a/diseases/d187/2026-2029.xlsx
+++ b/diseases/d187/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -909,6 +914,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1045,6 +1055,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1181,6 +1196,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1317,6 +1337,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1453,6 +1478,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1589,6 +1619,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1725,6 +1760,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1861,6 +1901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1997,6 +2042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2133,6 +2183,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2269,6 +2324,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2405,6 +2465,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2541,6 +2606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2677,6 +2747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2813,6 +2888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2949,6 +3029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3085,6 +3170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3221,6 +3311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3357,6 +3452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3493,6 +3593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3629,6 +3734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3765,6 +3875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3901,6 +4016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4037,6 +4157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4173,6 +4298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4309,6 +4439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4445,6 +4580,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4581,6 +4721,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4717,6 +4862,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4853,6 +5003,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4989,6 +5144,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5125,6 +5285,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5261,6 +5426,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5397,6 +5567,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5533,6 +5708,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5669,6 +5849,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5805,6 +5990,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5941,6 +6131,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6077,6 +6272,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6213,6 +6413,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6349,6 +6554,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6485,6 +6695,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6621,6 +6836,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6757,6 +6977,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6893,6 +7118,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7029,6 +7259,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7165,6 +7400,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7301,6 +7541,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7437,6 +7682,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7573,6 +7823,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7709,6 +7964,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7845,6 +8105,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7981,6 +8246,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8117,6 +8387,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8253,6 +8528,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8389,6 +8669,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8525,6 +8810,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8661,6 +8951,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8797,6 +9092,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8933,6 +9233,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9069,6 +9374,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9205,6 +9515,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9341,6 +9656,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9477,6 +9797,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9613,6 +9938,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9749,6 +10079,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9885,6 +10220,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10021,6 +10361,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10157,6 +10502,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10293,6 +10643,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10429,6 +10784,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10565,6 +10925,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10701,6 +11066,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10837,6 +11207,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10973,6 +11348,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11109,6 +11489,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11245,6 +11630,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11381,6 +11771,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11517,6 +11912,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11653,6 +12053,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11789,6 +12194,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11934,6 +12344,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12070,6 +12485,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12206,6 +12626,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12342,6 +12767,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12478,6 +12908,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12614,6 +13049,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12750,6 +13190,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12886,6 +13331,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13022,6 +13472,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13158,6 +13613,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13294,6 +13754,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13430,6 +13895,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13566,6 +14036,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13702,6 +14177,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13838,6 +14318,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13974,6 +14459,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14110,6 +14600,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14246,6 +14741,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14382,6 +14882,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14518,6 +15023,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14654,6 +15164,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14790,6 +15305,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14926,6 +15446,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15062,6 +15587,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15198,6 +15728,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15334,6 +15869,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15470,6 +16010,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15606,6 +16151,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15751,6 +16301,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15887,6 +16442,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16023,6 +16583,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16159,6 +16724,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16295,6 +16865,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16431,6 +17006,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16567,6 +17147,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16703,6 +17288,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16839,6 +17429,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16975,6 +17570,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17111,6 +17711,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17247,6 +17852,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17383,6 +17993,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17519,6 +18134,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17655,6 +18275,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17791,6 +18416,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17927,6 +18557,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18063,6 +18698,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18199,6 +18839,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18335,6 +18980,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18471,6 +19121,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18607,6 +19262,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18743,6 +19403,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18879,6 +19544,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19015,6 +19685,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19151,6 +19826,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19285,6 +19965,11 @@
       <c r="S138" t="inlineStr">
         <is>
           <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">

--- a/diseases/d187/2026-2029.xlsx
+++ b/diseases/d187/2026-2029.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>29.39871186333767</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,23 +780,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>all</t>
@@ -909,11 +894,6 @@
       <c r="R3" t="n">
         <v>34.95669839882178</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -926,23 +906,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>all</t>
@@ -1050,11 +1020,6 @@
       <c r="R4" t="n">
         <v>25.95778969879333</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1067,23 +1032,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>all</t>
@@ -1191,11 +1146,6 @@
       <c r="R5" t="n">
         <v>23.08775941320052</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1208,23 +1158,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>all</t>
@@ -1332,11 +1272,6 @@
       <c r="R6" t="n">
         <v>32.79498426807881</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1349,23 +1284,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>all</t>
@@ -1473,11 +1398,6 @@
       <c r="R7" t="n">
         <v>53.65391088204728</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1490,23 +1410,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>all</t>
@@ -1614,11 +1524,6 @@
       <c r="R8" t="n">
         <v>42.09307919346072</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1631,23 +1536,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>all</t>
@@ -1755,11 +1650,6 @@
       <c r="R9" t="n">
         <v>0.2409236821233664</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1772,23 +1662,13 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>all</t>
@@ -1896,11 +1776,6 @@
       <c r="R10" t="n">
         <v>44.46945063484043</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1913,23 +1788,13 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>all</t>
@@ -2037,11 +1902,6 @@
       <c r="R11" t="n">
         <v>36.40087196957758</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2054,23 +1914,13 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>all</t>
@@ -2178,11 +2028,6 @@
       <c r="R12" t="n">
         <v>36.50925655271259</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2195,23 +2040,13 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>all</t>
@@ -2319,11 +2154,6 @@
       <c r="R13" t="n">
         <v>29.49445018984719</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2336,23 +2166,13 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>all</t>
@@ -2460,11 +2280,6 @@
       <c r="R14" t="n">
         <v>27.59263150167201</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2477,23 +2292,13 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>all</t>
@@ -2601,11 +2406,6 @@
       <c r="R15" t="n">
         <v>25.27316257370102</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2618,23 +2418,13 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>all</t>
@@ -2742,11 +2532,6 @@
       <c r="R16" t="n">
         <v>51.54407496554963</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2759,23 +2544,13 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>all</t>
@@ -2883,11 +2658,6 @@
       <c r="R17" t="n">
         <v>42.04242935744893</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2900,23 +2670,13 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>all</t>
@@ -3024,11 +2784,6 @@
       <c r="R18" t="n">
         <v>43.24095528614046</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3041,23 +2796,13 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>all</t>
@@ -3165,11 +2910,6 @@
       <c r="R19" t="n">
         <v>39.27226337415507</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3182,23 +2922,13 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>all</t>
@@ -3306,11 +3036,6 @@
       <c r="R20" t="n">
         <v>27.01241944313662</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3323,23 +3048,13 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>all</t>
@@ -3447,11 +3162,6 @@
       <c r="R21" t="n">
         <v>36.92543631343835</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3464,23 +3174,13 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>all</t>
@@ -3588,11 +3288,6 @@
       <c r="R22" t="n">
         <v>28.28141199928528</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3605,23 +3300,13 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>all</t>
@@ -3729,11 +3414,6 @@
       <c r="R23" t="n">
         <v>67.9358538367332</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3746,23 +3426,13 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>all</t>
@@ -3870,11 +3540,6 @@
       <c r="R24" t="n">
         <v>35.27008095649754</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3887,23 +3552,13 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>all</t>
@@ -4011,11 +3666,6 @@
       <c r="R25" t="n">
         <v>43.84825784074818</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4028,23 +3678,13 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>all</t>
@@ -4152,11 +3792,6 @@
       <c r="R26" t="n">
         <v>25.83156174761784</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4169,23 +3804,13 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>all</t>
@@ -4293,11 +3918,6 @@
       <c r="R27" t="n">
         <v>33.08429665704382</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4310,23 +3930,13 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>all</t>
@@ -4434,11 +4044,6 @@
       <c r="R28" t="n">
         <v>47.93251102447753</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4451,23 +4056,13 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>all</t>
@@ -4575,11 +4170,6 @@
       <c r="R29" t="n">
         <v>22.97830352536737</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4592,23 +4182,13 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>all</t>
@@ -4716,11 +4296,6 @@
       <c r="R30" t="n">
         <v>33.80803246564557</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4733,23 +4308,13 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>all</t>
@@ -4857,11 +4422,6 @@
       <c r="R31" t="n">
         <v>24.3984878440955</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4874,23 +4434,13 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>all</t>
@@ -4998,11 +4548,6 @@
       <c r="R32" t="n">
         <v>16.29724193872978</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5015,23 +4560,13 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>all</t>
@@ -5139,11 +4674,6 @@
       <c r="R33" t="n">
         <v>27.71085502561811</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5156,23 +4686,13 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>all</t>
@@ -5280,11 +4800,6 @@
       <c r="R34" t="n">
         <v>50.98787804318779</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5297,23 +4812,13 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>all</t>
@@ -5421,11 +4926,6 @@
       <c r="R35" t="n">
         <v>36.91034805361868</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5438,23 +4938,13 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>all</t>
@@ -5562,11 +5052,6 @@
       <c r="R36" t="n">
         <v>0.1204618410616832</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5579,23 +5064,13 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>all</t>
@@ -5703,11 +5178,6 @@
       <c r="R37" t="n">
         <v>39.03918768603153</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5720,23 +5190,13 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>all</t>
@@ -5844,11 +5304,6 @@
       <c r="R38" t="n">
         <v>30.08018868663177</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5861,23 +5316,13 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>all</t>
@@ -5985,11 +5430,6 @@
       <c r="R39" t="n">
         <v>31.91938830709397</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6002,23 +5442,13 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>all</t>
@@ -6126,11 +5556,6 @@
       <c r="R40" t="n">
         <v>21.62021262477866</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6143,23 +5568,13 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>all</t>
@@ -6267,11 +5682,6 @@
       <c r="R41" t="n">
         <v>22.12473388299205</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6284,23 +5694,13 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>all</t>
@@ -6408,11 +5808,6 @@
       <c r="R42" t="n">
         <v>20.95628256789036</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6425,23 +5820,13 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>all</t>
@@ -6549,11 +5934,6 @@
       <c r="R43" t="n">
         <v>42.72229219083357</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6566,23 +5946,13 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>all</t>
@@ -6690,11 +6060,6 @@
       <c r="R44" t="n">
         <v>37.60757393999651</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6707,23 +6072,13 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>all</t>
@@ -6831,11 +6186,6 @@
       <c r="R45" t="n">
         <v>39.43858089492566</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6848,23 +6198,13 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>all</t>
@@ -6972,11 +6312,6 @@
       <c r="R46" t="n">
         <v>34.82966178666543</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6989,23 +6324,13 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>all</t>
@@ -7113,11 +6438,6 @@
       <c r="R47" t="n">
         <v>22.55388986386971</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7130,23 +6450,13 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>all</t>
@@ -7254,11 +6564,6 @@
       <c r="R48" t="n">
         <v>33.72080501493041</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7271,23 +6576,13 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>all</t>
@@ -7395,11 +6690,6 @@
       <c r="R49" t="n">
         <v>19.68887032545816</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7412,23 +6702,13 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>all</t>
@@ -7536,11 +6816,6 @@
       <c r="R50" t="n">
         <v>66.88462205589398</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7553,23 +6828,13 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>all</t>
@@ -7677,11 +6942,6 @@
       <c r="R51" t="n">
         <v>27.9792691686703</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7694,23 +6954,13 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>all</t>
@@ -7818,11 +7068,6 @@
       <c r="R52" t="n">
         <v>37.54469484800413</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7835,23 +7080,13 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>all</t>
@@ -7959,11 +7194,6 @@
       <c r="R53" t="n">
         <v>22.58094575588741</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7976,23 +7206,13 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
       </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV53" t="inlineStr">
         <is>
           <t>all</t>
@@ -8100,11 +7320,6 @@
       <c r="R54" t="n">
         <v>28.38952278922925</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8117,23 +7332,13 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>all</t>
@@ -8241,11 +7446,6 @@
       <c r="R55" t="n">
         <v>44.92498092098091</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8258,23 +7458,13 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>all</t>
@@ -8382,11 +7572,6 @@
       <c r="R56" t="n">
         <v>9.236376907255512</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8399,23 +7584,13 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>all</t>
@@ -8523,11 +7698,6 @@
       <c r="R57" t="n">
         <v>33.00086180990014</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8540,23 +7710,13 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV57" t="inlineStr">
         <is>
           <t>all</t>
@@ -8664,11 +7824,6 @@
       <c r="R58" t="n">
         <v>21.99074233316502</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8681,23 +7836,13 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>all</t>
@@ -8805,11 +7950,6 @@
       <c r="R59" t="n">
         <v>12.09946749996605</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8822,23 +7962,13 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
       </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV59" t="inlineStr">
         <is>
           <t>all</t>
@@ -8946,11 +8076,6 @@
       <c r="R60" t="n">
         <v>27.79144888415116</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8963,23 +8088,13 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
       </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>all</t>
@@ -9087,11 +8202,6 @@
       <c r="R61" t="n">
         <v>52.27789393295851</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9104,23 +8214,13 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
       </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV61" t="inlineStr">
         <is>
           <t>all</t>
@@ -9228,11 +8328,6 @@
       <c r="R62" t="n">
         <v>41.5947396607836</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9245,23 +8340,13 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
       </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV62" t="inlineStr">
         <is>
           <t>all</t>
@@ -9369,11 +8454,6 @@
       <c r="R63" t="n">
         <v>0.2650160503357031</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9386,23 +8466,13 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
       </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV63" t="inlineStr">
         <is>
           <t>all</t>
@@ -9510,11 +8580,6 @@
       <c r="R64" t="n">
         <v>36.87775624203389</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9527,23 +8592,13 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>all</t>
@@ -9651,11 +8706,6 @@
       <c r="R65" t="n">
         <v>26.10840797505096</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9668,23 +8718,13 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
       </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV65" t="inlineStr">
         <is>
           <t>all</t>
@@ -9792,11 +8832,6 @@
       <c r="R66" t="n">
         <v>34.82242172538879</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9809,23 +8844,13 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
       </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV66" t="inlineStr">
         <is>
           <t>all</t>
@@ -9933,11 +8958,6 @@
       <c r="R67" t="n">
         <v>22.67237367873179</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9950,23 +8970,13 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
       </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV67" t="inlineStr">
         <is>
           <t>all</t>
@@ -10074,11 +9084,6 @@
       <c r="R68" t="n">
         <v>21.92221915637428</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10091,23 +9096,13 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV68" t="inlineStr">
         <is>
           <t>all</t>
@@ -10215,11 +9210,6 @@
       <c r="R69" t="n">
         <v>21.21894986983122</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10232,23 +9222,13 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
       </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>all</t>
@@ -10356,11 +9336,6 @@
       <c r="R70" t="n">
         <v>46.30838274966123</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10373,23 +9348,13 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>all</t>
@@ -10497,11 +9462,6 @@
       <c r="R71" t="n">
         <v>39.18325198243254</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10514,23 +9474,13 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
       </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV71" t="inlineStr">
         <is>
           <t>all</t>
@@ -10638,11 +9588,6 @@
       <c r="R72" t="n">
         <v>39.20277473112939</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10655,23 +9600,13 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
       </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV72" t="inlineStr">
         <is>
           <t>all</t>
@@ -10779,11 +9714,6 @@
       <c r="R73" t="n">
         <v>34.40297123871446</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10796,23 +9726,13 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
       </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV73" t="inlineStr">
         <is>
           <t>all</t>
@@ -10920,11 +9840,6 @@
       <c r="R74" t="n">
         <v>20.61489392705312</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10937,23 +9852,13 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
       </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV74" t="inlineStr">
         <is>
           <t>all</t>
@@ -11061,11 +9966,6 @@
       <c r="R75" t="n">
         <v>36.26141361194571</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11078,23 +9978,13 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
       </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV75" t="inlineStr">
         <is>
           <t>all</t>
@@ -11202,11 +10092,6 @@
       <c r="R76" t="n">
         <v>17.41270034563641</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11219,23 +10104,13 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
       </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV76" t="inlineStr">
         <is>
           <t>all</t>
@@ -11343,11 +10218,6 @@
       <c r="R77" t="n">
         <v>68.19866178194299</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11360,23 +10230,13 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
       </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV77" t="inlineStr">
         <is>
           <t>all</t>
@@ -11484,11 +10344,6 @@
       <c r="R78" t="n">
         <v>29.83090390843595</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11501,23 +10356,13 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
       </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV78" t="inlineStr">
         <is>
           <t>all</t>
@@ -11625,11 +10470,6 @@
       <c r="R79" t="n">
         <v>39.98672402267406</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11642,23 +10482,13 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
       </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV79" t="inlineStr">
         <is>
           <t>all</t>
@@ -11766,11 +10596,6 @@
       <c r="R80" t="n">
         <v>25.87490329417425</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11783,23 +10608,13 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
       </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV80" t="inlineStr">
         <is>
           <t>all</t>
@@ -11907,11 +10722,6 @@
       <c r="R81" t="n">
         <v>29.17992521623678</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11924,23 +10734,13 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
       </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV81" t="inlineStr">
         <is>
           <t>all</t>
@@ -12048,11 +10848,6 @@
       <c r="R82" t="n">
         <v>46.74203035851012</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12065,23 +10860,13 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
       </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV82" t="inlineStr">
         <is>
           <t>all</t>
@@ -12189,11 +10974,6 @@
       <c r="R83" t="n">
         <v>23.50615816014859</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12206,23 +10986,13 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
       </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV83" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -12339,11 +11109,6 @@
       <c r="R84" t="n">
         <v>8.785821936169876</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12356,23 +11121,13 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
       </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV84" t="inlineStr">
         <is>
           <t>all</t>
@@ -12480,11 +11235,6 @@
       <c r="R85" t="n">
         <v>27.00917194225129</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12497,23 +11247,13 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
       </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV85" t="inlineStr">
         <is>
           <t>all</t>
@@ -12621,11 +11361,6 @@
       <c r="R86" t="n">
         <v>14.35474942707122</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12638,23 +11373,13 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
       </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV86" t="inlineStr">
         <is>
           <t>all</t>
@@ -12762,11 +11487,6 @@
       <c r="R87" t="n">
         <v>6.420125612226882</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12779,23 +11499,13 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
       </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV87" t="inlineStr">
         <is>
           <t>all</t>
@@ -12903,11 +11613,6 @@
       <c r="R88" t="n">
         <v>19.54401069426774</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12920,23 +11625,13 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
       </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV88" t="inlineStr">
         <is>
           <t>all</t>
@@ -13044,11 +11739,6 @@
       <c r="R89" t="n">
         <v>42.81777740797322</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13061,23 +11751,13 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
       </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV89" t="inlineStr">
         <is>
           <t>all</t>
@@ -13185,11 +11865,6 @@
       <c r="R90" t="n">
         <v>36.87712541810686</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13202,23 +11877,13 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
       </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV90" t="inlineStr">
         <is>
           <t>all</t>
@@ -13326,11 +11991,6 @@
       <c r="R91" t="n">
         <v>0.1927389456986931</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13343,23 +12003,13 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
       </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV91" t="inlineStr">
         <is>
           <t>all</t>
@@ -13467,11 +12117,6 @@
       <c r="R92" t="n">
         <v>31.86110054485417</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13484,23 +12129,13 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
       </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV92" t="inlineStr">
         <is>
           <t>all</t>
@@ -13608,11 +12243,6 @@
       <c r="R93" t="n">
         <v>14.40660243770532</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13625,23 +12255,13 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
       </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV93" t="inlineStr">
         <is>
           <t>all</t>
@@ -13749,11 +12369,6 @@
       <c r="R94" t="n">
         <v>25.76849888149338</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13766,23 +12381,13 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
       </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV94" t="inlineStr">
         <is>
           <t>all</t>
@@ -13890,11 +12495,6 @@
       <c r="R95" t="n">
         <v>10.75919529364966</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13907,23 +12507,13 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
       </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV95" t="inlineStr">
         <is>
           <t>all</t>
@@ -14031,11 +12621,6 @@
       <c r="R96" t="n">
         <v>15.59363394956877</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14048,23 +12633,13 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
       </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV96" t="inlineStr">
         <is>
           <t>all</t>
@@ -14172,11 +12747,6 @@
       <c r="R97" t="n">
         <v>15.17760192519144</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14189,23 +12759,13 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
       </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV97" t="inlineStr">
         <is>
           <t>all</t>
@@ -14313,11 +12873,6 @@
       <c r="R98" t="n">
         <v>35.02415112455018</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14330,23 +12885,13 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
       </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV98" t="inlineStr">
         <is>
           <t>all</t>
@@ -14454,11 +12999,6 @@
       <c r="R99" t="n">
         <v>32.87010485876498</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14471,23 +13011,13 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
       </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV99" t="inlineStr">
         <is>
           <t>all</t>
@@ -14595,11 +13125,6 @@
       <c r="R100" t="n">
         <v>29.53472201548244</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14612,23 +13137,13 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
       </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV100" t="inlineStr">
         <is>
           <t>all</t>
@@ -14736,11 +13251,6 @@
       <c r="R101" t="n">
         <v>27.74325209814619</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14753,23 +13263,13 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
       </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV101" t="inlineStr">
         <is>
           <t>all</t>
@@ -14877,11 +13377,6 @@
       <c r="R102" t="n">
         <v>11.52947883388552</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14894,23 +13389,13 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
       </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV102" t="inlineStr">
         <is>
           <t>all</t>
@@ -15018,11 +13503,6 @@
       <c r="R103" t="n">
         <v>29.27473997015363</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15035,23 +13515,13 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
       </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV103" t="inlineStr">
         <is>
           <t>all</t>
@@ -15159,11 +13629,6 @@
       <c r="R104" t="n">
         <v>8.76325442231375</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15176,23 +13641,13 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
       </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV104" t="inlineStr">
         <is>
           <t>all</t>
@@ -15300,11 +13755,6 @@
       <c r="R105" t="n">
         <v>62.5482909599323</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15317,23 +13767,13 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
       </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV105" t="inlineStr">
         <is>
           <t>all</t>
@@ -15441,11 +13881,6 @@
       <c r="R106" t="n">
         <v>20.1721361553315</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15458,23 +13893,13 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
       </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV106" t="inlineStr">
         <is>
           <t>all</t>
@@ -15582,11 +14007,6 @@
       <c r="R107" t="n">
         <v>29.55697380376359</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15599,23 +14019,13 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
       </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV107" t="inlineStr">
         <is>
           <t>all</t>
@@ -15723,11 +14133,6 @@
       <c r="R108" t="n">
         <v>21.49740709197726</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15740,23 +14145,13 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
       </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV108" t="inlineStr">
         <is>
           <t>all</t>
@@ -15864,11 +14259,6 @@
       <c r="R109" t="n">
         <v>23.91995947595929</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15881,23 +14271,13 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
       </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV109" t="inlineStr">
         <is>
           <t>all</t>
@@ -16005,11 +14385,6 @@
       <c r="R110" t="n">
         <v>42.23073520326518</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16022,23 +14397,13 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
       </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV110" t="inlineStr">
         <is>
           <t>all</t>
@@ -16146,11 +14511,6 @@
       <c r="R111" t="n">
         <v>6.731183733068189</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16163,23 +14523,13 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
       </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV111" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -16296,11 +14646,6 @@
       <c r="R112" t="n">
         <v>4.167633482542121</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16313,23 +14658,13 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
       </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV112" t="inlineStr">
         <is>
           <t>all</t>
@@ -16437,11 +14772,6 @@
       <c r="R113" t="n">
         <v>10.33799339858584</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16454,23 +14784,13 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
       </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV113" t="inlineStr">
         <is>
           <t>all</t>
@@ -16578,11 +14898,6 @@
       <c r="R114" t="n">
         <v>3.118603709395665</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16595,23 +14910,13 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
       </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV114" t="inlineStr">
         <is>
           <t>all</t>
@@ -16719,11 +15024,6 @@
       <c r="R115" t="n">
         <v>1.358103494894148</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16736,23 +15036,13 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
       </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV115" t="inlineStr">
         <is>
           <t>all</t>
@@ -16860,11 +15150,6 @@
       <c r="R116" t="n">
         <v>4.493107613218252</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16877,23 +15162,13 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
       </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV116" t="inlineStr">
         <is>
           <t>all</t>
@@ -17001,11 +15276,6 @@
       <c r="R117" t="n">
         <v>9.5568677167181</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17018,23 +15288,13 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
       </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV117" t="inlineStr">
         <is>
           <t>all</t>
@@ -17142,11 +15402,6 @@
       <c r="R118" t="n">
         <v>23.62129384889548</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17159,23 +15414,13 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
       </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV118" t="inlineStr">
         <is>
           <t>all</t>
@@ -17283,11 +15528,6 @@
       <c r="R119" t="n">
         <v>0.07227710463700993</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17300,23 +15540,13 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
       </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV119" t="inlineStr">
         <is>
           <t>all</t>
@@ -17424,11 +15654,6 @@
       <c r="R120" t="n">
         <v>11.0339740999139</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17441,23 +15666,13 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
       </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV120" t="inlineStr">
         <is>
           <t>all</t>
@@ -17565,11 +15780,6 @@
       <c r="R121" t="n">
         <v>1.181569172262393</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17582,23 +15792,13 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
       </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV121" t="inlineStr">
         <is>
           <t>all</t>
@@ -17706,11 +15906,6 @@
       <c r="R122" t="n">
         <v>9.086541196909961</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17723,23 +15918,13 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
       </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV122" t="inlineStr">
         <is>
           <t>all</t>
@@ -17847,11 +16032,6 @@
       <c r="R123" t="n">
         <v>2.613432295302915</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17864,23 +16044,13 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
       </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV123" t="inlineStr">
         <is>
           <t>all</t>
@@ -17988,11 +16158,6 @@
       <c r="R124" t="n">
         <v>2.885834854303311</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18005,23 +16170,13 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
       </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV124" t="inlineStr">
         <is>
           <t>all</t>
@@ -18129,11 +16284,6 @@
       <c r="R125" t="n">
         <v>0.8793644456280969</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18146,23 +16296,13 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
       </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV125" t="inlineStr">
         <is>
           <t>all</t>
@@ -18270,11 +16410,6 @@
       <c r="R126" t="n">
         <v>10.16058991667838</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18287,23 +16422,13 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
       </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV126" t="inlineStr">
         <is>
           <t>all</t>
@@ -18411,11 +16536,6 @@
       <c r="R127" t="n">
         <v>7.200118207158044</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18428,23 +16548,13 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
       </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV127" t="inlineStr">
         <is>
           <t>all</t>
@@ -18552,11 +16662,6 @@
       <c r="R128" t="n">
         <v>7.486845700531478</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18569,23 +16674,13 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
       </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV128" t="inlineStr">
         <is>
           <t>all</t>
@@ -18693,11 +16788,6 @@
       <c r="R129" t="n">
         <v>8.023455597744931</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18710,23 +16800,13 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
       </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV129" t="inlineStr">
         <is>
           <t>all</t>
@@ -18834,11 +16914,6 @@
       <c r="R130" t="n">
         <v>1.004330230746322</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18851,23 +16926,13 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
       </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV130" t="inlineStr">
         <is>
           <t>all</t>
@@ -18975,11 +17040,6 @@
       <c r="R131" t="n">
         <v>12.6453018805989</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18992,23 +17052,13 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
       </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV131" t="inlineStr">
         <is>
           <t>all</t>
@@ -19116,11 +17166,6 @@
       <c r="R132" t="n">
         <v>0.05690424949554383</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19133,23 +17178,13 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
       </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV132" t="inlineStr">
         <is>
           <t>all</t>
@@ -19257,11 +17292,6 @@
       <c r="R133" t="n">
         <v>24.57254287711626</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19274,23 +17304,13 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
       </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV133" t="inlineStr">
         <is>
           <t>all</t>
@@ -19398,11 +17418,6 @@
       <c r="R134" t="n">
         <v>6.080127534903537</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19415,23 +17430,13 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
       </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV134" t="inlineStr">
         <is>
           <t>all</t>
@@ -19539,11 +17544,6 @@
       <c r="R135" t="n">
         <v>8.769651568149635</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19556,23 +17556,13 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
       </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV135" t="inlineStr">
         <is>
           <t>all</t>
@@ -19680,11 +17670,6 @@
       <c r="R136" t="n">
         <v>10.87872818565785</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19697,23 +17682,13 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
       </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV136" t="inlineStr">
         <is>
           <t>all</t>
@@ -19821,11 +17796,6 @@
       <c r="R137" t="n">
         <v>6.985858163085704</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19838,23 +17808,13 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
       </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV137" t="inlineStr">
         <is>
           <t>all</t>
@@ -19962,11 +17922,6 @@
       <c r="R138" t="n">
         <v>29.63670289487304</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19979,22 +17934,12 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>

--- a/diseases/d187/2026-2029.xlsx
+++ b/diseases/d187/2026-2029.xlsx
@@ -17973,6 +17973,276 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D187</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>rabies-post-exposure-prophylaxis</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Rabies post-exposure prophylaxis</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D187</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Rabies post-exposure prophylaxis</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>狂犬病暴露后处置</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>53431</v>
+      </c>
+      <c r="O139" t="n">
+        <v>53431</v>
+      </c>
+      <c r="R139" t="n">
+        <v>24.94305278046788</v>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
+      <c r="AT139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D187</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>rabies-post-exposure-prophylaxis</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Rabies post-exposure prophylaxis</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D187</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Rabies post-exposure prophylaxis</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>狂犬病暴露后处置</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>4434</v>
+      </c>
+      <c r="O140" t="n">
+        <v>4434</v>
+      </c>
+      <c r="R140" t="n">
+        <v>2.069912523227988</v>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18006,7 +18276,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -18089,7 +18359,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -18099,7 +18369,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -18151,7 +18421,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>336110</v>
+        <v>393975</v>
       </c>
     </row>
     <row r="16">
